--- a/Context Data/CME Attendance Report 4.16.25.xlsx
+++ b/Context Data/CME Attendance Report 4.16.25.xlsx
@@ -3468,9 +3468,9 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B4ED48AFA98C9D4CBDAB85A9D631CF97" ma:contentTypeVersion="7" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e58c25bcd981d8c8d65677a9b5215e90">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="603e6958-f347-4390-937b-f81c7f882348" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3c75a39d0b2707d4d405c626d1715ccf" ns2:_="">
-    <xsd:import namespace="603e6958-f347-4390-937b-f81c7f882348"/>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D9425BFD98FC2C4FA733E6DF42251950" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="582fb54fea41c52898da559f243d0357">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="fff059bb-b667-4476-9a60-571bf927bc8d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9a69b03041c30401314916452ea380b9" ns2:_="">
+    <xsd:import namespace="fff059bb-b667-4476-9a60-571bf927bc8d"/>
     <xsd:element name="properties">
       <xsd:complexType>
         <xsd:sequence>
@@ -3480,10 +3480,6 @@
                 <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -3491,7 +3487,7 @@
       </xsd:complexType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="603e6958-f347-4390-937b-f81c7f882348" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="fff059bb-b667-4476-9a60-571bf927bc8d" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
@@ -3507,26 +3503,6 @@
     <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="12" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="13" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="14" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
@@ -3645,7 +3621,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B9BC9CA9-7C02-4DD2-8A09-88992C6DA1F4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F9960FF-041D-494F-ABA1-FE67A803D2D3}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
